--- a/ЛР1_Спрос_и_границы_рынка/Excel/XLT_C_финмодели_TableMind.xlsx
+++ b/ЛР1_Спрос_и_границы_рынка/Excel/XLT_C_финмодели_TableMind.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\ЛР1_Спрос_и_границы_рынка\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-project-continuation-447426\ЛР1_Спрос_и_границы_рынка\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AE637BD-D323-49AF-ABDF-CA4D32C9ED51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6D0946D-AC97-40A0-865D-86447ABCC506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Панель" sheetId="1" r:id="rId1"/>
@@ -42,12 +42,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="248">
   <si>
     <t>Панель оценки тренда, сезонности и циклов спроса</t>
-  </si>
-  <si>
-    <t>Файл предназначен для анализа интереса аудитории на основе выгрузок из Google Trends и Яндекс Вордстат. Заполните лист «Ввод_данных», после чего показатели на этой панели обновятся автоматически.</t>
   </si>
   <si>
     <t>Блок</t>
@@ -57,9 +54,6 @@
   </si>
   <si>
     <t>Значение</t>
-  </si>
-  <si>
-    <t>Как использовать</t>
   </si>
   <si>
     <t>Данные</t>
@@ -122,22 +116,13 @@
     <t>значение выше 1 означает спрос выше трендово-сезонного уровня</t>
   </si>
   <si>
-    <t>Итоговая формулировка для отчета</t>
-  </si>
-  <si>
     <t>Ввод данных из Google Trends и Яндекс Вордстат</t>
-  </si>
-  <si>
-    <t>Заполните строки по месяцам. Google Trends вводится как индекс 0–100. Яндекс Вордстат вводится как абсолютное число запросов по выбранному семантическому кластеру. В демонстрационном примере приведены условные данные для бизнеса на основе компетенции «маркетинг».</t>
   </si>
   <si>
     <t>Период</t>
   </si>
   <si>
     <t>Кластер запросов</t>
-  </si>
-  <si>
-    <t>Google Trends, 0–100</t>
   </si>
   <si>
     <t>Яндекс Вордстат, запросов</t>
@@ -152,9 +137,6 @@
     <t>Расчет тренда, сезонности и циклических отклонений</t>
   </si>
   <si>
-    <t>Расчет построен по мультипликативной логике: наблюдаемый интерес = тренд × сезонность × циклическое отклонение × случайные колебания. Для практической оценки используются скользящее среднее, сезонные индексы и коэффициент отклонения от трендово-сезонного уровня.</t>
-  </si>
-  <si>
     <t>Месяц №</t>
   </si>
   <si>
@@ -167,13 +149,7 @@
     <t>Вордстат</t>
   </si>
   <si>
-    <t>Вордстат норм. 0–100</t>
-  </si>
-  <si>
     <t>Сводный индекс</t>
-  </si>
-  <si>
-    <t>Тренд: скользящее среднее 12 мес.</t>
   </si>
   <si>
     <t>Y/T</t>
@@ -330,9 +306,6 @@
   </si>
   <si>
     <t>Оценка циклических отклонений и фаз спроса</t>
-  </si>
-  <si>
-    <t>Важно: данные Google Trends и Яндекс Вордстат не измеряют макроэкономический деловой цикл напрямую. В таблице оценивается поисковый цикл спроса: периоды, когда интерес находится выше или ниже трендово-сезонного уровня.</t>
   </si>
   <si>
     <t>Последний период</t>
@@ -593,12 +566,6 @@
     <t>аудит и проверка финансовых моделей</t>
   </si>
   <si>
-    <t>GT: мир; Вордстат: Россия</t>
-  </si>
-  <si>
-    <t>разовый выброс Вордстата 1069 заменен на 56 (правило: значение &gt; 3 x второго по величине заменяется средним трех предыдущих месяцев)</t>
-  </si>
-  <si>
     <t>индекс запроса financial model audit</t>
   </si>
   <si>
@@ -633,6 +600,195 @@
   </si>
   <si>
     <t>вкладка «Динамика», все устройства; значения запросов кластера суммированы</t>
+  </si>
+  <si>
+    <t>Производится анализ интереса аудитории на основе выгрузок из Google Trends и Яндекс Вордстат.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Trends вводится как индекс 0-100. 
+Яндекс Вордстат вводится как абсолютное число запросов по выбранному семантическому кластеру. </t>
+  </si>
+  <si>
+    <t>Расчет построен по мультипликативной логике. 
+Наблюдаемый интерес = тренд × сезонность × циклическое отклонение × случайные колебания. 
+Для практической оценки используются скользящее среднее, сезонные индексы и коэффициент отклонения от трендово-сезонного уровня.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В таблице оценивается поисковый цикл спроса, то есть периоды, когда интерес находится выше или ниже трендово-сезонного уровня. </t>
+  </si>
+  <si>
+    <t>Использование</t>
+  </si>
+  <si>
+    <t>Вывод:</t>
+  </si>
+  <si>
+    <t>Google Trends, 0-100</t>
+  </si>
+  <si>
+    <t>Вордстат норм. 0-100</t>
+  </si>
+  <si>
+    <t>Скользящее среднее 12 мес. (тренд)</t>
+  </si>
+  <si>
+    <t>Google Trends - весь мир, Вордстат - Россия</t>
+  </si>
+  <si>
+    <t>Google Trends ниже медианы ряда; Вордстат в нижней четверти значений ряда; начало ряда</t>
+  </si>
+  <si>
+    <t>Google Trends нулевое значение, ниже порога учета выгрузки; Вордстат выше медианы ряда, рост к предыдущему месяцу на 170 %</t>
+  </si>
+  <si>
+    <t>Google Trends нулевое значение, ниже порога учета выгрузки; Вордстат выше медианы ряда</t>
+  </si>
+  <si>
+    <t>Google Trends нулевое значение, ниже порога учета выгрузки; Вордстат в верхней четверти значений ряда</t>
+  </si>
+  <si>
+    <t>Google Trends выше медианы ряда; Вордстат выше медианы ряда</t>
+  </si>
+  <si>
+    <t>Google Trends выше медианы ряда, снижение к предыдущему месяцу на 56 %; Вордстат в верхней четверти значений ряда</t>
+  </si>
+  <si>
+    <t>Google Trends выше медианы ряда; Вордстат ниже медианы ряда, снижение к предыдущему месяцу на 47 %</t>
+  </si>
+  <si>
+    <t>Google Trends ниже медианы ряда; Вордстат ниже медианы ряда, рост к предыдущему месяцу на 30 %</t>
+  </si>
+  <si>
+    <t>Google Trends нулевое значение, ниже порога учета выгрузки; Вордстат в нижней четверти значений ряда, снижение к предыдущему месяцу на 38 %</t>
+  </si>
+  <si>
+    <t>Google Trends нулевое значение, ниже порога учета выгрузки; Вордстат в нижней четверти значений ряда</t>
+  </si>
+  <si>
+    <t>Google Trends выше медианы ряда; Вордстат в нижней четверти значений ряда, снижение к предыдущему месяцу на 39 %</t>
+  </si>
+  <si>
+    <t>Google Trends выше медианы ряда; Вордстат выше медианы ряда, рост к предыдущему месяцу на 154 %</t>
+  </si>
+  <si>
+    <t>Google Trends ниже медианы ряда; Вордстат выше медианы ряда</t>
+  </si>
+  <si>
+    <t>Google Trends нулевое значение, ниже порога учета выгрузки; Вордстат ниже медианы ряда</t>
+  </si>
+  <si>
+    <t>Google Trends ниже медианы ряда; Вордстат ниже медианы ряда</t>
+  </si>
+  <si>
+    <t>Google Trends ниже медианы ряда; Вордстат в верхней четверти значений ряда, рост к предыдущему месяцу на 31 %</t>
+  </si>
+  <si>
+    <t>Google Trends ниже медианы ряда; Вордстат в нижней четверти значений ряда, снижение к предыдущему месяцу на 35 %</t>
+  </si>
+  <si>
+    <t>Google Trends нулевое значение, ниже порога учета выгрузки; Вордстат ниже медианы ряда, рост к предыдущему месяцу на 39 %</t>
+  </si>
+  <si>
+    <t>Google Trends нулевое значение, ниже порога учета выгрузки; Вордстат в нижней четверти значений ряда, снижение к предыдущему месяцу на 48 %</t>
+  </si>
+  <si>
+    <t>Google Trends ниже медианы ряда; Вордстат ниже медианы ряда, рост к предыдущему месяцу на 38 %</t>
+  </si>
+  <si>
+    <t>Google Trends ниже медианы ряда; Вордстат в нижней четверти значений ряда, снижение к предыдущему месяцу на 33 %</t>
+  </si>
+  <si>
+    <t>Google Trends выше медианы ряда; Вордстат в нижней четверти значений ряда</t>
+  </si>
+  <si>
+    <t>Google Trends выше медианы ряда; Вордстат ниже медианы ряда, рост к предыдущему месяцу на 77 %</t>
+  </si>
+  <si>
+    <t>Google Trends нулевое значение, ниже порога учета выгрузки; Вордстат ниже медианы ряда, снижение к предыдущему месяцу на 35 %</t>
+  </si>
+  <si>
+    <t>Google Trends выше медианы ряда; Вордстат в нижней четверти значений ряда, снижение к предыдущему месяцу на 61 %</t>
+  </si>
+  <si>
+    <t>Google Trends нулевое значение, ниже порога учета выгрузки; Вордстат в нижней четверти значений ряда, рост к предыдущему месяцу на 60 %</t>
+  </si>
+  <si>
+    <t>Google Trends выше медианы ряда; Вордстат минимум ряда, снижение к предыдущему месяцу на 44 %</t>
+  </si>
+  <si>
+    <t>Google Trends выше медианы ряда; Вордстат выше медианы ряда, рост к предыдущему месяцу на 306 %</t>
+  </si>
+  <si>
+    <t>Google Trends ниже медианы ряда, снижение к предыдущему месяцу на 75 %; Вордстат ниже медианы ряда, снижение к предыдущему месяцу на 30 %</t>
+  </si>
+  <si>
+    <t>Google Trends выше медианы ряда; Вордстат ниже медианы ряда</t>
+  </si>
+  <si>
+    <t>Google Trends выше медианы ряда; Вордстат в верхней четверти значений ряда, рост к предыдущему месяцу на 61 %</t>
+  </si>
+  <si>
+    <t>Google Trends выше медианы ряда; Вордстат в верхней четверти значений ряда</t>
+  </si>
+  <si>
+    <t>Google Trends выше медианы ряда, снижение к предыдущему месяцу на 25 %; Вордстат в верхней четверти значений ряда</t>
+  </si>
+  <si>
+    <t>Google Trends нулевое значение, ниже порога учета выгрузки; Вордстат в верхней четверти значений ряда, снижение к предыдущему месяцу на 32 %</t>
+  </si>
+  <si>
+    <t>Google Trends в верхней четверти значений ряда; Вордстат в верхней четверти значений ряда</t>
+  </si>
+  <si>
+    <t>Google Trends выше медианы ряда; Вордстат в нижней четверти значений ряда, снижение к предыдущему месяцу на 56 %</t>
+  </si>
+  <si>
+    <t>Google Trends в верхней четверти значений ряда, рост к предыдущему месяцу на 160 %; Вордстат минимум ряда, снижение к предыдущему месяцу на 57 %</t>
+  </si>
+  <si>
+    <t>Google Trends в верхней четверти значений ряда; Вордстат выше медианы ряда, рост к предыдущему месяцу на 306 %</t>
+  </si>
+  <si>
+    <t>Google Trends в верхней четверти значений ряда; Вордстат в верхней четверти значений ряда, рост к предыдущему месяцу на 85 %</t>
+  </si>
+  <si>
+    <t>Google Trends в верхней четверти значений ряда, рост к предыдущему месяцу на 31 %; Вордстат в верхней четверти значений ряда</t>
+  </si>
+  <si>
+    <t>Google Trends в верхней четверти значений ряда; Вордстат максимум ряда</t>
+  </si>
+  <si>
+    <t>Google Trends в верхней четверти значений ряда; Вордстат в верхней четверти значений ряда, снижение к предыдущему месяцу на 38 %</t>
+  </si>
+  <si>
+    <t>Google Trends в верхней четверти значений ряда, рост к предыдущему месяцу на 62 %; Вордстат выше медианы ряда</t>
+  </si>
+  <si>
+    <t>Google Trends в верхней четверти значений ряда, рост к предыдущему месяцу на 39 %; Вордстат в верхней четверти значений ряда</t>
+  </si>
+  <si>
+    <t>Google Trends максимум ряда, рост к предыдущему месяцу на 32 %; Вордстат в верхней четверти значений ряда</t>
+  </si>
+  <si>
+    <t>Google Trends в верхней четверти значений ряда, снижение к предыдущему месяцу на 28 %; Вордстат в верхней четверти значений ряда</t>
+  </si>
+  <si>
+    <t>Google Trends в верхней четверти значений ряда, снижение к предыдущему месяцу на 47 %; Вордстат ниже медианы ряда, снижение к предыдущему месяцу на 34 %</t>
+  </si>
+  <si>
+    <t>Google Trends в верхней четверти значений ряда; Вордстат в нижней четверти значений ряда, снижение к предыдущему месяцу на 44 %</t>
+  </si>
+  <si>
+    <t>Google Trends в верхней четверти значений ряда, рост к предыдущему месяцу на 53 %; Вордстат ниже медианы ряда, рост к предыдущему месяцу на 82 %; разовый выброс Вордстата 1069 заменен на 56 по правилу, значение больше 3 x второго по величине заменяется средним трех предыдущих месяцев; конец ряда, выгрузка от 02.10.2026</t>
+  </si>
+  <si>
+    <t>https://otexts.com/fpp3/moving-averages.html</t>
+  </si>
+  <si>
+    <t>https://otexts.com/fpp3/classical-decomposition.html</t>
+  </si>
+  <si>
+    <t>https://otexts.com/fpp3/tspatterns.html</t>
   </si>
 </sst>
 </file>
@@ -1960,7 +2116,7 @@
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Период"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Кластер запросов"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Google Trends, 0–100"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Google Trends, 0-100"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Яндекс Вордстат, запросов"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Регион / рынок"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Комментарий"/>
@@ -1977,9 +2133,9 @@
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Месяц"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Google Trends"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Вордстат"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Вордстат норм. 0–100"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Вордстат норм. 0-100"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Сводный индекс"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Тренд: скользящее среднее 12 мес."/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Скользящее среднее 12 мес. (тренд)"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Y/T"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Сезонно очищенный индекс"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Циклический коэффициент"/>
@@ -2294,7 +2450,7 @@
     </row>
     <row r="3" spans="1:26">
       <c r="A3" s="12" t="s">
-        <v>1</v>
+        <v>186</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -2352,16 +2508,16 @@
     </row>
     <row r="5" spans="1:26">
       <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>5</v>
+        <v>190</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -2388,17 +2544,17 @@
     </row>
     <row r="6" spans="1:26">
       <c r="A6" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C6" s="3">
         <f>Оценка_тренда!B4</f>
         <v>60</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
@@ -2425,17 +2581,17 @@
     </row>
     <row r="7" spans="1:26">
       <c r="A7" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C7" s="3" t="str">
         <f>Оценка_тренда!B10</f>
         <v>растущий тренд</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
@@ -2462,17 +2618,17 @@
     </row>
     <row r="8" spans="1:26" ht="26.25">
       <c r="A8" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C8" s="4">
         <f>Оценка_тренда!B8</f>
         <v>1.0974486295776034</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
@@ -2499,17 +2655,17 @@
     </row>
     <row r="9" spans="1:26">
       <c r="A9" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C9" s="3" t="str">
         <f>Сезонность!B22</f>
         <v>выраженная сезонность</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -2536,17 +2692,17 @@
     </row>
     <row r="10" spans="1:26">
       <c r="A10" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C10" s="3" t="str">
         <f>Сезонность!B23</f>
         <v>апрель</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
@@ -2573,17 +2729,17 @@
     </row>
     <row r="11" spans="1:26">
       <c r="A11" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C11" s="3" t="str">
         <f>Сезонность!B24</f>
         <v>август</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -2610,17 +2766,17 @@
     </row>
     <row r="12" spans="1:26">
       <c r="A12" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C12" s="3" t="str">
         <f>Деловые_циклы!B7</f>
         <v>выше тренда</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
@@ -2647,17 +2803,17 @@
     </row>
     <row r="13" spans="1:26" ht="26.25">
       <c r="A13" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C13" s="5">
         <f>Деловые_циклы!B6</f>
         <v>1.2162574407075661</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
@@ -2740,7 +2896,7 @@
     </row>
     <row r="16" spans="1:26">
       <c r="A16" s="13" t="s">
-        <v>26</v>
+        <v>191</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -2770,8 +2926,8 @@
     </row>
     <row r="17" spans="1:26">
       <c r="A17" s="14" t="str">
-        <f>Оценка_тренда!B11&amp;" Сезонность: "&amp;Сезонность!B22&amp;"; максимум интереса — "&amp;Сезонность!B23&amp;", минимум — "&amp;Сезонность!B24&amp;". Текущая фаза спроса: "&amp;Деловые_циклы!B7&amp;"."</f>
-        <v>Интерес аудитории растет; бизнес-идея может быть дополнительно проверена на платежеспособный спрос. Сезонность: выраженная сезонность; максимум интереса — апрель, минимум — август. Текущая фаза спроса: выше тренда.</v>
+        <f>Оценка_тренда!B11&amp;" Для ряда характерна "&amp;Сезонность!B22&amp;", максимум интереса приходится на "&amp;Сезонность!B23&amp;", минимум на "&amp;Сезонность!B24&amp;". Текущая фаза спроса - "&amp;Деловые_циклы!B7&amp;"."</f>
+        <v>Интерес аудитории растет; бизнес-идея может быть дополнительно проверена на платежеспособный спрос. Для ряда характерна выраженная сезонность, максимум интереса приходится на апрель, минимум на август. Текущая фаза спроса - выше тренда.</v>
       </c>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
@@ -5150,7 +5306,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="14" customHeight="1">
       <c r="A1" s="11" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -5180,7 +5336,7 @@
     </row>
     <row r="2" spans="1:26">
       <c r="A2" s="12" t="s">
-        <v>28</v>
+        <v>187</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
@@ -5236,24 +5392,24 @@
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
     </row>
-    <row r="4" spans="1:26" ht="26.25">
+    <row r="4" spans="1:26">
       <c r="A4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -5276,12 +5432,12 @@
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:26" ht="26.25">
       <c r="A5" s="6">
         <v>44470</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C5" s="7">
         <v>0.6</v>
@@ -5290,9 +5446,11 @@
         <v>30</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F5" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>196</v>
+      </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
@@ -5314,12 +5472,12 @@
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:26" ht="39.4">
       <c r="A6" s="6">
         <v>44501</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C6" s="7">
         <v>0</v>
@@ -5328,9 +5486,11 @@
         <v>81</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F6" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>197</v>
+      </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -5352,12 +5512,12 @@
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:26" ht="26.25">
       <c r="A7" s="6">
         <v>44531</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C7" s="7">
         <v>0</v>
@@ -5366,9 +5526,11 @@
         <v>79</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F7" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>198</v>
+      </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -5390,12 +5552,12 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" spans="1:26" ht="26.25">
       <c r="A8" s="6">
         <v>44562</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C8" s="7">
         <v>0</v>
@@ -5404,9 +5566,11 @@
         <v>86</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F8" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>199</v>
+      </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -5428,12 +5592,12 @@
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9" spans="1:26" ht="26.25">
       <c r="A9" s="6">
         <v>44593</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C9" s="7">
         <v>2</v>
@@ -5442,9 +5606,11 @@
         <v>74</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F9" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>200</v>
+      </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -5466,12 +5632,12 @@
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
     </row>
-    <row r="10" spans="1:26">
+    <row r="10" spans="1:26" ht="26.25">
       <c r="A10" s="6">
         <v>44621</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C10" s="7">
         <v>2.25</v>
@@ -5480,9 +5646,11 @@
         <v>78</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F10" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>200</v>
+      </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -5504,12 +5672,12 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:26" ht="39.4">
       <c r="A11" s="6">
         <v>44652</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C11" s="7">
         <v>1</v>
@@ -5518,9 +5686,11 @@
         <v>95</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F11" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>201</v>
+      </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -5542,12 +5712,12 @@
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
     </row>
-    <row r="12" spans="1:26">
+    <row r="12" spans="1:26" ht="39.4">
       <c r="A12" s="6">
         <v>44682</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C12" s="7">
         <v>1</v>
@@ -5556,9 +5726,11 @@
         <v>50</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F12" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>202</v>
+      </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -5580,12 +5752,12 @@
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" spans="1:26" ht="26.25">
       <c r="A13" s="6">
         <v>44713</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C13" s="7">
         <v>0.75</v>
@@ -5594,9 +5766,11 @@
         <v>65</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F13" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>203</v>
+      </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -5618,12 +5792,12 @@
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:26" ht="39.4">
       <c r="A14" s="6">
         <v>44743</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C14" s="7">
         <v>0</v>
@@ -5632,9 +5806,11 @@
         <v>40</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F14" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>204</v>
+      </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -5656,12 +5832,12 @@
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:26" ht="26.25">
       <c r="A15" s="6">
         <v>44774</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C15" s="7">
         <v>0</v>
@@ -5670,9 +5846,11 @@
         <v>46</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F15" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>205</v>
+      </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -5694,12 +5872,12 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" spans="1:26" ht="39.4">
       <c r="A16" s="6">
         <v>44805</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C16" s="7">
         <v>1.25</v>
@@ -5708,9 +5886,11 @@
         <v>28</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F16" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -5732,12 +5912,12 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26">
+    <row r="17" spans="1:26" ht="26.25">
       <c r="A17" s="6">
         <v>44835</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C17" s="7">
         <v>0.8</v>
@@ -5746,9 +5926,11 @@
         <v>71</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F17" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>207</v>
+      </c>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -5770,12 +5952,12 @@
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
     </row>
-    <row r="18" spans="1:26">
+    <row r="18" spans="1:26" ht="26.25">
       <c r="A18" s="6">
         <v>44866</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C18" s="7">
         <v>0.5</v>
@@ -5784,9 +5966,11 @@
         <v>69</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F18" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>208</v>
+      </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -5808,12 +5992,12 @@
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
-    <row r="19" spans="1:26">
+    <row r="19" spans="1:26" ht="26.25">
       <c r="A19" s="6">
         <v>44896</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C19" s="7">
         <v>0</v>
@@ -5822,9 +6006,11 @@
         <v>62</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F19" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>209</v>
+      </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -5846,12 +6032,12 @@
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
     </row>
-    <row r="20" spans="1:26">
+    <row r="20" spans="1:26" ht="26.25">
       <c r="A20" s="6">
         <v>44927</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C20" s="7">
         <v>0.4</v>
@@ -5860,9 +6046,11 @@
         <v>66</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F20" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>210</v>
+      </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -5884,12 +6072,12 @@
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
     </row>
-    <row r="21" spans="1:26">
+    <row r="21" spans="1:26" ht="26.25">
       <c r="A21" s="6">
         <v>44958</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C21" s="7">
         <v>0.5</v>
@@ -5898,9 +6086,11 @@
         <v>71</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F21" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>208</v>
+      </c>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -5922,12 +6112,12 @@
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
     </row>
-    <row r="22" spans="1:26">
+    <row r="22" spans="1:26" ht="39.4">
       <c r="A22" s="6">
         <v>44986</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C22" s="7">
         <v>0.75</v>
@@ -5936,9 +6126,11 @@
         <v>93</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F22" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -5960,12 +6152,12 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
     </row>
-    <row r="23" spans="1:26">
+    <row r="23" spans="1:26" ht="26.25">
       <c r="A23" s="6">
         <v>45017</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C23" s="7">
         <v>0.8</v>
@@ -5974,9 +6166,11 @@
         <v>71</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F23" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>200</v>
+      </c>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -5998,12 +6192,12 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
     </row>
-    <row r="24" spans="1:26">
+    <row r="24" spans="1:26" ht="39.4">
       <c r="A24" s="6">
         <v>45047</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C24" s="7">
         <v>0.5</v>
@@ -6012,9 +6206,11 @@
         <v>46</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F24" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>212</v>
+      </c>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -6036,12 +6232,12 @@
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
     </row>
-    <row r="25" spans="1:26">
+    <row r="25" spans="1:26" ht="39.4">
       <c r="A25" s="6">
         <v>45078</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C25" s="7">
         <v>0</v>
@@ -6050,9 +6246,11 @@
         <v>64</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F25" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>213</v>
+      </c>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
@@ -6074,12 +6272,12 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
-    <row r="26" spans="1:26">
+    <row r="26" spans="1:26" ht="39.4">
       <c r="A26" s="6">
         <v>45108</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C26" s="7">
         <v>0</v>
@@ -6088,9 +6286,11 @@
         <v>33</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F26" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>214</v>
+      </c>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -6112,12 +6312,12 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
-    <row r="27" spans="1:26">
+    <row r="27" spans="1:26" ht="26.25">
       <c r="A27" s="6">
         <v>45139</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C27" s="7">
         <v>0</v>
@@ -6126,9 +6326,11 @@
         <v>37</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F27" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>205</v>
+      </c>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -6150,12 +6352,12 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" spans="1:26">
+    <row r="28" spans="1:26" ht="26.25">
       <c r="A28" s="6">
         <v>45170</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C28" s="7">
         <v>0</v>
@@ -6164,9 +6366,11 @@
         <v>37</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F28" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>205</v>
+      </c>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -6188,12 +6392,12 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
-    <row r="29" spans="1:26">
+    <row r="29" spans="1:26" ht="26.25">
       <c r="A29" s="6">
         <v>45200</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C29" s="7">
         <v>0.4</v>
@@ -6202,9 +6406,11 @@
         <v>51</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F29" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>215</v>
+      </c>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -6226,12 +6432,12 @@
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
     </row>
-    <row r="30" spans="1:26">
+    <row r="30" spans="1:26" ht="26.25">
       <c r="A30" s="6">
         <v>45231</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C30" s="7">
         <v>0</v>
@@ -6240,9 +6446,11 @@
         <v>57</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F30" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>209</v>
+      </c>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
@@ -6264,12 +6472,12 @@
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
     </row>
-    <row r="31" spans="1:26">
+    <row r="31" spans="1:26" ht="26.25">
       <c r="A31" s="6">
         <v>45261</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C31" s="7">
         <v>0</v>
@@ -6278,9 +6486,11 @@
         <v>69</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F31" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>198</v>
+      </c>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -6302,12 +6512,12 @@
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
     </row>
-    <row r="32" spans="1:26">
+    <row r="32" spans="1:26" ht="39.4">
       <c r="A32" s="6">
         <v>45292</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C32" s="7">
         <v>0.75</v>
@@ -6316,9 +6526,11 @@
         <v>46</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F32" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>216</v>
+      </c>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -6340,12 +6552,12 @@
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
     </row>
-    <row r="33" spans="1:26">
+    <row r="33" spans="1:26" ht="26.25">
       <c r="A33" s="6">
         <v>45323</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C33" s="7">
         <v>1</v>
@@ -6354,9 +6566,11 @@
         <v>35</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F33" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>217</v>
+      </c>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -6378,12 +6592,12 @@
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
     </row>
-    <row r="34" spans="1:26">
+    <row r="34" spans="1:26" ht="26.25">
       <c r="A34" s="6">
         <v>45352</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C34" s="7">
         <v>0.8</v>
@@ -6392,9 +6606,11 @@
         <v>62</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F34" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>218</v>
+      </c>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -6416,12 +6632,12 @@
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
     </row>
-    <row r="35" spans="1:26">
+    <row r="35" spans="1:26" ht="26.25">
       <c r="A35" s="6">
         <v>45383</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C35" s="7">
         <v>0</v>
@@ -6430,9 +6646,11 @@
         <v>77</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F35" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>198</v>
+      </c>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -6454,12 +6672,12 @@
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
     </row>
-    <row r="36" spans="1:26">
+    <row r="36" spans="1:26" ht="26.25">
       <c r="A36" s="6">
         <v>45413</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C36" s="7">
         <v>0.75</v>
@@ -6468,9 +6686,11 @@
         <v>79</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F36" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>208</v>
+      </c>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -6492,12 +6712,12 @@
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
     </row>
-    <row r="37" spans="1:26">
+    <row r="37" spans="1:26" ht="39.4">
       <c r="A37" s="6">
         <v>45444</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C37" s="7">
         <v>0</v>
@@ -6506,9 +6726,11 @@
         <v>51</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F37" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>219</v>
+      </c>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -6530,12 +6752,12 @@
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
     </row>
-    <row r="38" spans="1:26">
+    <row r="38" spans="1:26" ht="39.4">
       <c r="A38" s="6">
         <v>45474</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C38" s="7">
         <v>1.25</v>
@@ -6544,9 +6766,11 @@
         <v>20</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F38" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>220</v>
+      </c>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
@@ -6568,12 +6792,12 @@
       <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
     </row>
-    <row r="39" spans="1:26">
+    <row r="39" spans="1:26" ht="39.4">
       <c r="A39" s="6">
         <v>45505</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C39" s="7">
         <v>0</v>
@@ -6582,9 +6806,11 @@
         <v>32</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F39" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>221</v>
+      </c>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
@@ -6606,12 +6832,12 @@
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
     </row>
-    <row r="40" spans="1:26">
+    <row r="40" spans="1:26" ht="26.25">
       <c r="A40" s="6">
         <v>45536</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C40" s="7">
         <v>2.2000000000000002</v>
@@ -6620,9 +6846,11 @@
         <v>18</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F40" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>222</v>
+      </c>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -6644,12 +6872,12 @@
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
     </row>
-    <row r="41" spans="1:26">
+    <row r="41" spans="1:26" ht="26.25">
       <c r="A41" s="6">
         <v>45566</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C41" s="7">
         <v>2</v>
@@ -6658,9 +6886,11 @@
         <v>73</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F41" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>223</v>
+      </c>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -6682,12 +6912,12 @@
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
     </row>
-    <row r="42" spans="1:26">
+    <row r="42" spans="1:26" ht="39.4">
       <c r="A42" s="6">
         <v>45597</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C42" s="7">
         <v>0.5</v>
@@ -6696,9 +6926,11 @@
         <v>51</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F42" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>224</v>
+      </c>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
@@ -6720,12 +6952,12 @@
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
     </row>
-    <row r="43" spans="1:26">
+    <row r="43" spans="1:26" ht="26.25">
       <c r="A43" s="6">
         <v>45627</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C43" s="7">
         <v>0.8</v>
@@ -6734,9 +6966,11 @@
         <v>64</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F43" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>225</v>
+      </c>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
@@ -6758,12 +6992,12 @@
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
     </row>
-    <row r="44" spans="1:26">
+    <row r="44" spans="1:26" ht="26.25">
       <c r="A44" s="6">
         <v>45658</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C44" s="7">
         <v>0.75</v>
@@ -6772,9 +7006,11 @@
         <v>64</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F44" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>210</v>
+      </c>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
@@ -6796,12 +7032,12 @@
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
     </row>
-    <row r="45" spans="1:26">
+    <row r="45" spans="1:26" ht="39.4">
       <c r="A45" s="6">
         <v>45689</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C45" s="7">
         <v>2</v>
@@ -6810,9 +7046,11 @@
         <v>103</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F45" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>226</v>
+      </c>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
@@ -6834,12 +7072,12 @@
       <c r="Y45" s="1"/>
       <c r="Z45" s="1"/>
     </row>
-    <row r="46" spans="1:26">
+    <row r="46" spans="1:26" ht="26.25">
       <c r="A46" s="6">
         <v>45717</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C46" s="7">
         <v>2</v>
@@ -6848,9 +7086,11 @@
         <v>114</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F46" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>227</v>
+      </c>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
@@ -6872,12 +7112,12 @@
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
     </row>
-    <row r="47" spans="1:26">
+    <row r="47" spans="1:26" ht="39.4">
       <c r="A47" s="6">
         <v>45748</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C47" s="7">
         <v>1.5</v>
@@ -6886,9 +7126,11 @@
         <v>122</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F47" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>228</v>
+      </c>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
@@ -6910,12 +7152,12 @@
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
     </row>
-    <row r="48" spans="1:26">
+    <row r="48" spans="1:26" ht="39.4">
       <c r="A48" s="6">
         <v>45778</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C48" s="7">
         <v>0</v>
@@ -6924,9 +7166,11 @@
         <v>83</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F48" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>229</v>
+      </c>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
@@ -6948,12 +7192,12 @@
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
     </row>
-    <row r="49" spans="1:26">
+    <row r="49" spans="1:26" ht="26.25">
       <c r="A49" s="6">
         <v>45809</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C49" s="7">
         <v>5.2</v>
@@ -6962,9 +7206,11 @@
         <v>95</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F49" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>230</v>
+      </c>
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
@@ -6986,12 +7232,12 @@
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
     </row>
-    <row r="50" spans="1:26">
+    <row r="50" spans="1:26" ht="39.4">
       <c r="A50" s="6">
         <v>45839</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C50" s="7">
         <v>5</v>
@@ -7000,9 +7246,11 @@
         <v>42</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F50" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>231</v>
+      </c>
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
@@ -7024,12 +7272,12 @@
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
     </row>
-    <row r="51" spans="1:26">
+    <row r="51" spans="1:26" ht="39.4">
       <c r="A51" s="6">
         <v>45870</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C51" s="7">
         <v>13</v>
@@ -7038,9 +7286,11 @@
         <v>18</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F51" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>232</v>
+      </c>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
@@ -7062,12 +7312,12 @@
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
     </row>
-    <row r="52" spans="1:26">
+    <row r="52" spans="1:26" ht="39.4">
       <c r="A52" s="6">
         <v>45901</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C52" s="7">
         <v>12.75</v>
@@ -7076,9 +7326,11 @@
         <v>73</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F52" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>233</v>
+      </c>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
@@ -7100,12 +7352,12 @@
       <c r="Y52" s="1"/>
       <c r="Z52" s="1"/>
     </row>
-    <row r="53" spans="1:26">
+    <row r="53" spans="1:26" ht="39.4">
       <c r="A53" s="6">
         <v>45931</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C53" s="7">
         <v>13</v>
@@ -7114,9 +7366,11 @@
         <v>135</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F53" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>234</v>
+      </c>
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
@@ -7138,12 +7392,12 @@
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
     </row>
-    <row r="54" spans="1:26">
+    <row r="54" spans="1:26" ht="39.4">
       <c r="A54" s="6">
         <v>45962</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C54" s="7">
         <v>17</v>
@@ -7152,9 +7406,11 @@
         <v>130</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F54" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>235</v>
+      </c>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
@@ -7176,12 +7432,12 @@
       <c r="Y54" s="1"/>
       <c r="Z54" s="1"/>
     </row>
-    <row r="55" spans="1:26">
+    <row r="55" spans="1:26" ht="26.25">
       <c r="A55" s="6">
         <v>45992</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C55" s="7">
         <v>14.5</v>
@@ -7190,9 +7446,11 @@
         <v>150</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F55" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>236</v>
+      </c>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
@@ -7214,12 +7472,12 @@
       <c r="Y55" s="1"/>
       <c r="Z55" s="1"/>
     </row>
-    <row r="56" spans="1:26">
+    <row r="56" spans="1:26" ht="39.4">
       <c r="A56" s="6">
         <v>46023</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C56" s="7">
         <v>16.5</v>
@@ -7228,9 +7486,11 @@
         <v>93</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F56" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>237</v>
+      </c>
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
@@ -7252,12 +7512,12 @@
       <c r="Y56" s="1"/>
       <c r="Z56" s="1"/>
     </row>
-    <row r="57" spans="1:26">
+    <row r="57" spans="1:26" ht="39.4">
       <c r="A57" s="6">
         <v>46054</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C57" s="7">
         <v>26.75</v>
@@ -7266,9 +7526,11 @@
         <v>76</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F57" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>238</v>
+      </c>
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
@@ -7290,12 +7552,12 @@
       <c r="Y57" s="1"/>
       <c r="Z57" s="1"/>
     </row>
-    <row r="58" spans="1:26">
+    <row r="58" spans="1:26" ht="26.25">
       <c r="A58" s="6">
         <v>46082</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C58" s="7">
         <v>33.6</v>
@@ -7304,9 +7566,11 @@
         <v>86</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F58" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>230</v>
+      </c>
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
@@ -7328,12 +7592,12 @@
       <c r="Y58" s="1"/>
       <c r="Z58" s="1"/>
     </row>
-    <row r="59" spans="1:26">
+    <row r="59" spans="1:26" ht="39.4">
       <c r="A59" s="6">
         <v>46113</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C59" s="7">
         <v>46.75</v>
@@ -7342,9 +7606,11 @@
         <v>99</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F59" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>239</v>
+      </c>
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
@@ -7366,12 +7632,12 @@
       <c r="Y59" s="1"/>
       <c r="Z59" s="1"/>
     </row>
-    <row r="60" spans="1:26">
+    <row r="60" spans="1:26" ht="39.4">
       <c r="A60" s="6">
         <v>46143</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C60" s="7">
         <v>61.8</v>
@@ -7380,9 +7646,11 @@
         <v>88</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F60" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>240</v>
+      </c>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
@@ -7404,12 +7672,12 @@
       <c r="Y60" s="1"/>
       <c r="Z60" s="1"/>
     </row>
-    <row r="61" spans="1:26">
+    <row r="61" spans="1:26" ht="39.4">
       <c r="A61" s="6">
         <v>46174</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C61" s="7">
         <v>44.75</v>
@@ -7418,9 +7686,11 @@
         <v>83</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F61" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>241</v>
+      </c>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
@@ -7442,12 +7712,12 @@
       <c r="Y61" s="1"/>
       <c r="Z61" s="1"/>
     </row>
-    <row r="62" spans="1:26">
+    <row r="62" spans="1:26" ht="52.5">
       <c r="A62" s="6">
         <v>46204</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C62" s="7">
         <v>23.75</v>
@@ -7456,9 +7726,11 @@
         <v>55</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F62" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>242</v>
+      </c>
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
@@ -7480,12 +7752,12 @@
       <c r="Y62" s="1"/>
       <c r="Z62" s="1"/>
     </row>
-    <row r="63" spans="1:26">
+    <row r="63" spans="1:26" ht="39.4">
       <c r="A63" s="6">
         <v>46235</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C63" s="7">
         <v>19.8</v>
@@ -7494,9 +7766,11 @@
         <v>31</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F63" s="3"/>
+        <v>195</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>243</v>
+      </c>
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
@@ -7518,12 +7792,12 @@
       <c r="Y63" s="1"/>
       <c r="Z63" s="1"/>
     </row>
-    <row r="64" spans="1:26" ht="39.4">
+    <row r="64" spans="1:26" ht="91.9">
       <c r="A64" s="6">
         <v>46266</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C64" s="7">
         <v>30.33</v>
@@ -7532,10 +7806,10 @@
         <v>56.33</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>184</v>
+        <v>244</v>
       </c>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
@@ -8599,7 +8873,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="14" customHeight="1">
       <c r="A1" s="11" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -8629,7 +8903,7 @@
     </row>
     <row r="2" spans="1:26">
       <c r="A2" s="12" t="s">
-        <v>36</v>
+        <v>188</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
@@ -8687,46 +8961,46 @@
     </row>
     <row r="4" spans="1:26" ht="26.25">
       <c r="A4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="N4" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
@@ -8791,8 +9065,8 @@
         <v/>
       </c>
       <c r="M5" s="3" t="str">
-        <f t="shared" ref="M5:M36" si="4">IF(L5="","",IF(L5="ниже тренда","возможное ослабление интереса",IF(L5="выше тренда","возможная фаза повышенного интереса","без выраженного отклонения")))</f>
-        <v/>
+        <f>IF(G5="","","окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется")</f>
+        <v>окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется</v>
       </c>
       <c r="N5" s="7">
         <f>IF(G5="","",COUNT($G$5:G5))</f>
@@ -8861,8 +9135,8 @@
         <v/>
       </c>
       <c r="M6" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f>IF(G6="","","окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется")</f>
+        <v>окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется</v>
       </c>
       <c r="N6" s="7">
         <f>IF(G6="","",COUNT($G$5:G6))</f>
@@ -8931,8 +9205,8 @@
         <v/>
       </c>
       <c r="M7" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f>IF(G7="","","окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется")</f>
+        <v>окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется</v>
       </c>
       <c r="N7" s="7">
         <f>IF(G7="","",COUNT($G$5:G7))</f>
@@ -9001,8 +9275,8 @@
         <v/>
       </c>
       <c r="M8" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f>IF(G8="","","окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется")</f>
+        <v>окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется</v>
       </c>
       <c r="N8" s="7">
         <f>IF(G8="","",COUNT($G$5:G8))</f>
@@ -9071,8 +9345,8 @@
         <v/>
       </c>
       <c r="M9" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f>IF(G9="","","окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется")</f>
+        <v>окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется</v>
       </c>
       <c r="N9" s="7">
         <f>IF(G9="","",COUNT($G$5:G9))</f>
@@ -9141,8 +9415,8 @@
         <v/>
       </c>
       <c r="M10" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f>IF(G10="","","окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется")</f>
+        <v>окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется</v>
       </c>
       <c r="N10" s="7">
         <f>IF(G10="","",COUNT($G$5:G10))</f>
@@ -9211,8 +9485,8 @@
         <v/>
       </c>
       <c r="M11" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f>IF(G11="","","окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется")</f>
+        <v>окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется</v>
       </c>
       <c r="N11" s="7">
         <f>IF(G11="","",COUNT($G$5:G11))</f>
@@ -9281,8 +9555,8 @@
         <v/>
       </c>
       <c r="M12" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f>IF(G12="","","окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется")</f>
+        <v>окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется</v>
       </c>
       <c r="N12" s="7">
         <f>IF(G12="","",COUNT($G$5:G12))</f>
@@ -9351,8 +9625,8 @@
         <v/>
       </c>
       <c r="M13" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f>IF(G13="","","окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется")</f>
+        <v>окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется</v>
       </c>
       <c r="N13" s="7">
         <f>IF(G13="","",COUNT($G$5:G13))</f>
@@ -9421,8 +9695,8 @@
         <v/>
       </c>
       <c r="M14" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f>IF(G14="","","окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется")</f>
+        <v>окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется</v>
       </c>
       <c r="N14" s="7">
         <f>IF(G14="","",COUNT($G$5:G14))</f>
@@ -9491,8 +9765,8 @@
         <v/>
       </c>
       <c r="M15" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f>IF(G15="","","окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется")</f>
+        <v>окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется</v>
       </c>
       <c r="N15" s="7">
         <f>IF(G15="","",COUNT($G$5:G15))</f>
@@ -9561,7 +9835,7 @@
         <v>ниже тренда</v>
       </c>
       <c r="M16" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="M5:M36" si="4">IF(L16="","",IF(L16="ниже тренда","возможное ослабление интереса",IF(L16="выше тренда","возможная фаза повышенного интереса","без выраженного отклонения")))</f>
         <v>возможное ослабление интереса</v>
       </c>
       <c r="N16" s="7">
@@ -10987,7 +11261,7 @@
         <v>45444</v>
       </c>
       <c r="B37" s="3">
-        <f t="shared" ref="B37:B68" si="5">IF(A37="","",MONTH(A37))</f>
+        <f t="shared" ref="B37:B64" si="5">IF(A37="","",MONTH(A37))</f>
         <v>6</v>
       </c>
       <c r="C37" s="3" t="str">
@@ -11003,7 +11277,7 @@
         <v>51</v>
       </c>
       <c r="F37" s="5">
-        <f t="shared" ref="F37:F68" si="7">IF(E37="","",IF(MAX($E$5:$E$64)=0,"",E37/MAX($E$5:$E$64)*100))</f>
+        <f t="shared" ref="F37:F64" si="7">IF(E37="","",IF(MAX($E$5:$E$64)=0,"",E37/MAX($E$5:$E$64)*100))</f>
         <v>34</v>
       </c>
       <c r="G37" s="5">
@@ -11015,7 +11289,7 @@
         <v>17.765277777777779</v>
       </c>
       <c r="I37" s="5">
-        <f t="shared" ref="I37:I68" si="8">IF(OR(G37="",H37="",H37=0),"",G37/H37)</f>
+        <f t="shared" ref="I37:I64" si="8">IF(OR(G37="",H37="",H37=0),"",G37/H37)</f>
         <v>0.95692283636932207</v>
       </c>
       <c r="J37" s="5">
@@ -11031,7 +11305,7 @@
         <v>норма</v>
       </c>
       <c r="M37" s="3" t="str">
-        <f t="shared" ref="M37:M68" si="9">IF(L37="","",IF(L37="ниже тренда","возможное ослабление интереса",IF(L37="выше тренда","возможная фаза повышенного интереса","без выраженного отклонения")))</f>
+        <f t="shared" ref="M37:M64" si="9">IF(L37="","",IF(L37="ниже тренда","возможное ослабление интереса",IF(L37="выше тренда","возможная фаза повышенного интереса","без выраженного отклонения")))</f>
         <v>без выраженного отклонения</v>
       </c>
       <c r="N37" s="7">
@@ -13983,7 +14257,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="14" customHeight="1">
       <c r="A1" s="11" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -14041,22 +14315,22 @@
     </row>
     <row r="3" spans="1:26">
       <c r="A3" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -14084,7 +14358,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C4" s="5">
         <f>IFERROR(SUMIFS(Расчет!$I$5:$I$64,Расчет!$B$5:$B$64,A4)/COUNTIFS(Расчет!$B$5:$B$64,A4,Расчет!$I$5:$I$64,"&gt;0"),"")</f>
@@ -14128,7 +14402,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C5" s="5">
         <f>IFERROR(SUMIFS(Расчет!$I$5:$I$64,Расчет!$B$5:$B$64,A5)/COUNTIFS(Расчет!$B$5:$B$64,A5,Расчет!$I$5:$I$64,"&gt;0"),"")</f>
@@ -14172,7 +14446,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C6" s="5">
         <f>IFERROR(SUMIFS(Расчет!$I$5:$I$64,Расчет!$B$5:$B$64,A6)/COUNTIFS(Расчет!$B$5:$B$64,A6,Расчет!$I$5:$I$64,"&gt;0"),"")</f>
@@ -14216,7 +14490,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C7" s="5">
         <f>IFERROR(SUMIFS(Расчет!$I$5:$I$64,Расчет!$B$5:$B$64,A7)/COUNTIFS(Расчет!$B$5:$B$64,A7,Расчет!$I$5:$I$64,"&gt;0"),"")</f>
@@ -14260,7 +14534,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C8" s="5">
         <f>IFERROR(SUMIFS(Расчет!$I$5:$I$64,Расчет!$B$5:$B$64,A8)/COUNTIFS(Расчет!$B$5:$B$64,A8,Расчет!$I$5:$I$64,"&gt;0"),"")</f>
@@ -14304,7 +14578,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C9" s="5">
         <f>IFERROR(SUMIFS(Расчет!$I$5:$I$64,Расчет!$B$5:$B$64,A9)/COUNTIFS(Расчет!$B$5:$B$64,A9,Расчет!$I$5:$I$64,"&gt;0"),"")</f>
@@ -14348,7 +14622,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C10" s="5">
         <f>IFERROR(SUMIFS(Расчет!$I$5:$I$64,Расчет!$B$5:$B$64,A10)/COUNTIFS(Расчет!$B$5:$B$64,A10,Расчет!$I$5:$I$64,"&gt;0"),"")</f>
@@ -14392,7 +14666,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C11" s="5">
         <f>IFERROR(SUMIFS(Расчет!$I$5:$I$64,Расчет!$B$5:$B$64,A11)/COUNTIFS(Расчет!$B$5:$B$64,A11,Расчет!$I$5:$I$64,"&gt;0"),"")</f>
@@ -14436,7 +14710,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C12" s="5">
         <f>IFERROR(SUMIFS(Расчет!$I$5:$I$64,Расчет!$B$5:$B$64,A12)/COUNTIFS(Расчет!$B$5:$B$64,A12,Расчет!$I$5:$I$64,"&gt;0"),"")</f>
@@ -14480,7 +14754,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C13" s="5">
         <f>IFERROR(SUMIFS(Расчет!$I$5:$I$64,Расчет!$B$5:$B$64,A13)/COUNTIFS(Расчет!$B$5:$B$64,A13,Расчет!$I$5:$I$64,"&gt;0"),"")</f>
@@ -14524,7 +14798,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C14" s="5">
         <f>IFERROR(SUMIFS(Расчет!$I$5:$I$64,Расчет!$B$5:$B$64,A14)/COUNTIFS(Расчет!$B$5:$B$64,A14,Расчет!$I$5:$I$64,"&gt;0"),"")</f>
@@ -14568,7 +14842,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C15" s="5">
         <f>IFERROR(SUMIFS(Расчет!$I$5:$I$64,Расчет!$B$5:$B$64,A15)/COUNTIFS(Расчет!$B$5:$B$64,A15,Расчет!$I$5:$I$64,"&gt;0"),"")</f>
@@ -14665,10 +14939,10 @@
     </row>
     <row r="18" spans="1:26">
       <c r="A18" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>4</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -14697,7 +14971,7 @@
     </row>
     <row r="19" spans="1:26" ht="39.4">
       <c r="A19" s="3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B19" s="5">
         <f>MAX($D$4:$D$15)</f>
@@ -14730,7 +15004,7 @@
     </row>
     <row r="20" spans="1:26" ht="39.4">
       <c r="A20" s="3" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B20" s="5">
         <f>MIN($D$4:$D$15)</f>
@@ -14763,7 +15037,7 @@
     </row>
     <row r="21" spans="1:26" ht="26.25">
       <c r="A21" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="B21" s="5">
         <f>B19-B20</f>
@@ -14796,7 +15070,7 @@
     </row>
     <row r="22" spans="1:26" ht="39.4">
       <c r="A22" s="3" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="B22" s="3" t="str">
         <f>IF(B21&gt;=Настройки!$B$7,"выраженная сезонность",IF(B21&gt;=Настройки!$B$8,"умеренная сезонность","слабая сезонность"))</f>
@@ -14829,7 +15103,7 @@
     </row>
     <row r="23" spans="1:26" ht="26.25">
       <c r="A23" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B23" s="3" t="str">
         <f>IFERROR(INDEX($B$4:$B$15,MATCH(B19,$D$4:$D$15,0)),"")</f>
@@ -14862,7 +15136,7 @@
     </row>
     <row r="24" spans="1:26" ht="26.25">
       <c r="A24" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B24" s="3" t="str">
         <f>IFERROR(INDEX($B$4:$B$15,MATCH(B20,$D$4:$D$15,0)),"")</f>
@@ -17045,7 +17319,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="14" customHeight="1">
       <c r="A1" s="11" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -17103,16 +17377,16 @@
     </row>
     <row r="3" spans="1:26">
       <c r="A3" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -17139,17 +17413,17 @@
     </row>
     <row r="4" spans="1:26">
       <c r="A4" s="3" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B4" s="3">
         <f>COUNT(Расчет!$G$5:$G$64)</f>
         <v>60</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
@@ -17176,17 +17450,17 @@
     </row>
     <row r="5" spans="1:26">
       <c r="A5" s="3" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B5" s="5">
         <f>IF(B4&lt;12,"",SUMIFS(Расчет!$G$5:$G$64,Расчет!$N$5:$N$64,"&gt;=1",Расчет!$N$5:$N$64,"&lt;=12")/COUNTIFS(Расчет!$N$5:$N$64,"&gt;=1",Расчет!$N$5:$N$64,"&lt;=12"))</f>
         <v>21.257638888888888</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -17213,17 +17487,17 @@
     </row>
     <row r="6" spans="1:26">
       <c r="A6" s="3" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B6" s="5">
         <f>IF(B4&lt;12,"",SUMIFS(Расчет!$G$5:$G$64,Расчет!$N$5:$N$64,"&gt;="&amp;B4-11,Расчет!$N$5:$N$64,"&lt;="&amp;B4)/COUNTIFS(Расчет!$N$5:$N$64,"&gt;="&amp;B4-11,Расчет!$N$5:$N$64,"&lt;="&amp;B4))</f>
         <v>44.586805555555564</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
@@ -17250,17 +17524,17 @@
     </row>
     <row r="7" spans="1:26">
       <c r="A7" s="3" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B7" s="5">
         <f>IF(OR(B5="",B6=""),"",B6-B5)</f>
         <v>23.329166666666676</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
@@ -17287,17 +17561,17 @@
     </row>
     <row r="8" spans="1:26">
       <c r="A8" s="3" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B8" s="4">
         <f>IF(OR(B5="",B6=""),"",B7/B5)</f>
         <v>1.0974486295776034</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
@@ -17324,17 +17598,17 @@
     </row>
     <row r="9" spans="1:26">
       <c r="A9" s="3" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B9" s="5">
         <f>IFERROR(SLOPE(Расчет!$G$5:$G$64,Расчет!$N$5:$N$64),"")</f>
         <v>0.39029776789849041</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -17361,17 +17635,17 @@
     </row>
     <row r="10" spans="1:26">
       <c r="A10" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B10" s="3" t="str">
         <f>IF(B8="","",IF(B8&gt;=Настройки!$B$10,"растущий тренд",IF(B8&lt;=Настройки!$B$9,"снижающийся тренд","стабильный тренд")))</f>
         <v>растущий тренд</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
@@ -17398,17 +17672,17 @@
     </row>
     <row r="11" spans="1:26" ht="52.5">
       <c r="A11" s="3" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B11" s="3" t="str">
         <f>IF(B10="","Недостаточно данных",IF(B10="растущий тренд","Интерес аудитории растет; бизнес-идея может быть дополнительно проверена на платежеспособный спрос.",IF(B10="снижающийся тренд","Интерес аудитории снижается; требуется осторожная проверка ниши, сегмента и каналов продвижения.","Интерес аудитории относительно стабилен; целесообразно изучить структуру спроса, конкурентов и целевые сегменты.")))</f>
         <v>Интерес аудитории растет; бизнес-идея может быть дополнительно проверена на платежеспособный спрос.</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -19953,7 +20227,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="14" customHeight="1">
       <c r="A1" s="11" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -19983,7 +20257,7 @@
     </row>
     <row r="2" spans="1:26">
       <c r="A2" s="12" t="s">
-        <v>96</v>
+        <v>189</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
@@ -20041,10 +20315,10 @@
     </row>
     <row r="4" spans="1:26">
       <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>4</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -20073,7 +20347,7 @@
     </row>
     <row r="5" spans="1:26">
       <c r="A5" s="1" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="B5" s="8">
         <f>IFERROR(INDEX(Расчет!$A$5:$A$64,Оценка_тренда!$B$4),"")</f>
@@ -20106,7 +20380,7 @@
     </row>
     <row r="6" spans="1:26">
       <c r="A6" s="1" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="B6" s="9">
         <f>IFERROR(INDEX(Расчет!$K$5:$K$64,Оценка_тренда!$B$4),"")</f>
@@ -20139,7 +20413,7 @@
     </row>
     <row r="7" spans="1:26">
       <c r="A7" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B7" s="9" t="str">
         <f>IFERROR(INDEX(Расчет!$L$5:$L$64,Оценка_тренда!$B$4),"")</f>
@@ -20172,7 +20446,7 @@
     </row>
     <row r="8" spans="1:26">
       <c r="A8" s="1" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="B8" s="9">
         <f>MIN(Расчет!$K$5:$K$64)</f>
@@ -20205,7 +20479,7 @@
     </row>
     <row r="9" spans="1:26">
       <c r="A9" s="1" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="B9" s="9">
         <f>MAX(Расчет!$K$5:$K$64)</f>
@@ -20238,7 +20512,7 @@
     </row>
     <row r="10" spans="1:26">
       <c r="A10" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B10" s="9">
         <f>B9-B8</f>
@@ -20327,28 +20601,28 @@
     </row>
     <row r="13" spans="1:26" ht="26.25">
       <c r="A13" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -20399,8 +20673,8 @@
         <v/>
       </c>
       <c r="H14" s="3" t="str">
-        <f t="shared" ref="H14:H45" si="0">IF(G14="","",IF(G14="ниже тренда","период осторожного планирования продаж и бюджета",IF(G14="выше тренда","период активизации продвижения и продаж","обычный режим анализа спроса")))</f>
-        <v/>
+        <f>IF(B14="","","окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца")</f>
+        <v>окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
@@ -20451,8 +20725,8 @@
         <v/>
       </c>
       <c r="H15" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <f>IF(B15="","","окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца")</f>
+        <v>окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца</v>
       </c>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -20503,8 +20777,8 @@
         <v/>
       </c>
       <c r="H16" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <f>IF(B16="","","окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца")</f>
+        <v>окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -20555,8 +20829,8 @@
         <v/>
       </c>
       <c r="H17" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <f>IF(B17="","","окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца")</f>
+        <v>окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца</v>
       </c>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -20607,8 +20881,8 @@
         <v/>
       </c>
       <c r="H18" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <f>IF(B18="","","окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца")</f>
+        <v>окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца</v>
       </c>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
@@ -20659,8 +20933,8 @@
         <v/>
       </c>
       <c r="H19" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <f>IF(B19="","","окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца")</f>
+        <v>окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
@@ -20711,8 +20985,8 @@
         <v/>
       </c>
       <c r="H20" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <f>IF(B20="","","окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца")</f>
+        <v>окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца</v>
       </c>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -20763,8 +21037,8 @@
         <v/>
       </c>
       <c r="H21" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <f>IF(B21="","","окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца")</f>
+        <v>окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца</v>
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
@@ -20815,8 +21089,8 @@
         <v/>
       </c>
       <c r="H22" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <f>IF(B22="","","окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца")</f>
+        <v>окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца</v>
       </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -20867,8 +21141,8 @@
         <v/>
       </c>
       <c r="H23" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <f>IF(B23="","","окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца")</f>
+        <v>окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца</v>
       </c>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
@@ -20919,8 +21193,8 @@
         <v/>
       </c>
       <c r="H24" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <f>IF(B24="","","окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца")</f>
+        <v>окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца</v>
       </c>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
@@ -20971,7 +21245,7 @@
         <v>ниже тренда</v>
       </c>
       <c r="H25" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="H14:H45" si="0">IF(G25="","",IF(G25="ниже тренда","период осторожного планирования продаж и бюджета",IF(G25="выше тренда","период активизации продвижения и продаж","обычный режим анализа спроса")))</f>
         <v>период осторожного планирования продаж и бюджета</v>
       </c>
       <c r="I25" s="1"/>
@@ -22063,7 +22337,7 @@
         <v>норма</v>
       </c>
       <c r="H46" s="3" t="str">
-        <f t="shared" ref="H46:H77" si="1">IF(G46="","",IF(G46="ниже тренда","период осторожного планирования продаж и бюджета",IF(G46="выше тренда","период активизации продвижения и продаж","обычный режим анализа спроса")))</f>
+        <f t="shared" ref="H46:H73" si="1">IF(G46="","",IF(G46="ниже тренда","период осторожного планирования продаж и бюджета",IF(G46="выше тренда","период активизации продвижения и продаж","обычный режим анализа спроса")))</f>
         <v>обычный режим анализа спроса</v>
       </c>
       <c r="I46" s="1"/>
@@ -24274,7 +24548,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="14" customHeight="1">
       <c r="A1" s="11" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -24332,28 +24606,28 @@
     </row>
     <row r="3" spans="1:26">
       <c r="A3" s="2" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
@@ -24379,25 +24653,25 @@
         <v>46297</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -24423,25 +24697,25 @@
         <v>46297</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
@@ -27148,7 +27422,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="14" customHeight="1">
       <c r="A1" s="11" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -27206,22 +27480,22 @@
     </row>
     <row r="3" spans="1:26">
       <c r="A3" s="2" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -27246,22 +27520,22 @@
     </row>
     <row r="4" spans="1:26" ht="26.25">
       <c r="A4" s="3" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -27286,22 +27560,22 @@
     </row>
     <row r="5" spans="1:26" ht="26.25">
       <c r="A5" s="3" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
@@ -27326,21 +27600,23 @@
     </row>
     <row r="6" spans="1:26" ht="26.25">
       <c r="A6" s="3" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="F6" s="3"/>
+        <v>126</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>245</v>
+      </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -27364,21 +27640,23 @@
     </row>
     <row r="7" spans="1:26" ht="26.25">
       <c r="A7" s="3" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="F7" s="3"/>
+        <v>131</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>246</v>
+      </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -27402,21 +27680,23 @@
     </row>
     <row r="8" spans="1:26" ht="26.25">
       <c r="A8" s="3" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="F8" s="3"/>
+        <v>136</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>247</v>
+      </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -27440,22 +27720,22 @@
     </row>
     <row r="9" spans="1:26" ht="26.25">
       <c r="A9" s="3" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
@@ -30050,7 +30330,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="14" customHeight="1">
       <c r="A1" s="11" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -30108,16 +30388,16 @@
     </row>
     <row r="3" spans="1:26">
       <c r="A3" s="2" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -30144,16 +30424,16 @@
     </row>
     <row r="4" spans="1:26">
       <c r="A4" s="3" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="B4" s="5">
         <v>0.5</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
@@ -30180,16 +30460,16 @@
     </row>
     <row r="5" spans="1:26">
       <c r="A5" s="3" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="B5" s="5">
         <v>0.5</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -30216,16 +30496,16 @@
     </row>
     <row r="6" spans="1:26">
       <c r="A6" s="3" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="B6" s="5">
         <v>12</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
@@ -30252,16 +30532,16 @@
     </row>
     <row r="7" spans="1:26" ht="26.25">
       <c r="A7" s="3" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="B7" s="5">
         <v>0.3</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
@@ -30288,16 +30568,16 @@
     </row>
     <row r="8" spans="1:26">
       <c r="A8" s="3" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="B8" s="5">
         <v>0.15</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
@@ -30324,16 +30604,16 @@
     </row>
     <row r="9" spans="1:26">
       <c r="A9" s="3" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="B9" s="5">
         <v>-0.15</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -30360,16 +30640,16 @@
     </row>
     <row r="10" spans="1:26">
       <c r="A10" s="3" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="B10" s="5">
         <v>0.15</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
@@ -30396,16 +30676,16 @@
     </row>
     <row r="11" spans="1:26">
       <c r="A11" s="3" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="B11" s="5">
         <v>0.9</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -30432,16 +30712,16 @@
     </row>
     <row r="12" spans="1:26">
       <c r="A12" s="3" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="B12" s="5">
         <v>1.1000000000000001</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
